--- a/outputs/did/tables/did_panel_summary_post_from_0.xlsx
+++ b/outputs/did/tables/did_panel_summary_post_from_0.xlsx
@@ -62,17 +62,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.087***</t>
+          <t>-0.061</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.140*</t>
+          <t>0.100</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.059***</t>
+          <t>-0.091*</t>
         </is>
       </c>
     </row>
@@ -84,17 +84,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>(0.022)</t>
+          <t>(0.052)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(0.077)</t>
+          <t>(0.196)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(0.022)</t>
+          <t>(0.052)</t>
         </is>
       </c>
     </row>
@@ -128,17 +128,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.176***</t>
+          <t>-0.042</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.337*</t>
+          <t>0.252</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.125***</t>
+          <t>-0.091</t>
         </is>
       </c>
     </row>
@@ -150,17 +150,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>(0.036)</t>
+          <t>(0.075)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>(0.165)</t>
+          <t>(0.287)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>(0.033)</t>
+          <t>(0.072)</t>
         </is>
       </c>
     </row>
@@ -194,17 +194,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>-0.104</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.050</t>
+          <t>-0.053</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>-0.108</t>
         </is>
       </c>
     </row>
@@ -216,17 +216,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>(0.031)</t>
+          <t>(0.067)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>(0.064)</t>
+          <t>(0.203)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>(0.033)</t>
+          <t>(0.072)</t>
         </is>
       </c>
     </row>
@@ -260,17 +260,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>0.364</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.372</t>
         </is>
       </c>
     </row>
@@ -282,17 +282,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>0.353</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.453</t>
+          <t>0.407</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.342</t>
+          <t>0.356</t>
         </is>
       </c>
     </row>
@@ -304,17 +304,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>0.519</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>0.475</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.414</t>
+          <t>0.536</t>
         </is>
       </c>
     </row>
@@ -348,12 +348,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>9,458</t>
+          <t>9,548</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1,539</t>
+          <t>1,629</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -370,17 +370,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10,038</t>
+          <t>1,825</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1,411</t>
+          <t>253</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8,627</t>
+          <t>1,572</t>
         </is>
       </c>
     </row>
@@ -392,17 +392,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5,543</t>
+          <t>1,658</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>242</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4,726</t>
+          <t>1,416</t>
         </is>
       </c>
     </row>
@@ -414,17 +414,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5,323</t>
+          <t>1,039</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>180</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4,568</t>
+          <t>859</t>
         </is>
       </c>
     </row>
@@ -436,17 +436,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4,090</t>
+          <t>928</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>169</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3,491</t>
+          <t>759</t>
         </is>
       </c>
     </row>
@@ -458,17 +458,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4,714</t>
+          <t>784</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4,058</t>
+          <t>711</t>
         </is>
       </c>
     </row>
@@ -480,17 +480,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3,391</t>
+          <t>730</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2,921</t>
+          <t>657</t>
         </is>
       </c>
     </row>

--- a/outputs/did/tables/did_panel_summary_post_from_0.xlsx
+++ b/outputs/did/tables/did_panel_summary_post_from_0.xlsx
@@ -72,7 +72,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.091*</t>
+          <t>-0.091.</t>
         </is>
       </c>
     </row>

--- a/outputs/did/tables/did_panel_summary_post_from_0.xlsx
+++ b/outputs/did/tables/did_panel_summary_post_from_0.xlsx
@@ -62,17 +62,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.061</t>
+          <t>-0.059.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.100</t>
+          <t>0.041</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.091.</t>
+          <t>-0.078*</t>
         </is>
       </c>
     </row>
@@ -84,17 +84,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>(0.052)</t>
+          <t>(0.030)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(0.196)</t>
+          <t>(0.085)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(0.052)</t>
+          <t>(0.032)</t>
         </is>
       </c>
     </row>
@@ -128,17 +128,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.042</t>
+          <t>-0.063</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>0.213</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.091</t>
+          <t>-0.111.</t>
         </is>
       </c>
     </row>
@@ -150,17 +150,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>(0.075)</t>
+          <t>(0.062)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>(0.287)</t>
+          <t>(0.234)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>(0.072)</t>
+          <t>(0.060)</t>
         </is>
       </c>
     </row>
@@ -194,17 +194,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-0.104</t>
+          <t>-0.061</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.053</t>
+          <t>0.005</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.108</t>
+          <t>-0.070.</t>
         </is>
       </c>
     </row>
@@ -216,17 +216,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>(0.067)</t>
+          <t>(0.039)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>(0.203)</t>
+          <t>(0.156)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>(0.072)</t>
+          <t>(0.041)</t>
         </is>
       </c>
     </row>
@@ -260,17 +260,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.398</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.364</t>
+          <t>0.432</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>0.412</t>
         </is>
       </c>
     </row>
@@ -282,17 +282,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>0.369</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>0.410</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>0.387</t>
         </is>
       </c>
     </row>
@@ -304,17 +304,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0.519</t>
+          <t>0.462</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>0.506</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.536</t>
+          <t>0.466</t>
         </is>
       </c>
     </row>
@@ -370,17 +370,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1,825</t>
+          <t>3,887</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>567</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1,572</t>
+          <t>3,320</t>
         </is>
       </c>
     </row>
@@ -392,17 +392,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1,658</t>
+          <t>2,925</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>412</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1,416</t>
+          <t>2,513</t>
         </is>
       </c>
     </row>
@@ -414,17 +414,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1,039</t>
+          <t>1,373</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>215</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>1,158</t>
         </is>
       </c>
     </row>
@@ -436,17 +436,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>1,261</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>204</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>1,057</t>
         </is>
       </c>
     </row>
@@ -458,17 +458,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>2,512</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>352</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>2,160</t>
         </is>
       </c>
     </row>
@@ -480,17 +480,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>2,073</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>271</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>1,802</t>
         </is>
       </c>
     </row>

--- a/outputs/did/tables/did_panel_summary_post_from_0.xlsx
+++ b/outputs/did/tables/did_panel_summary_post_from_0.xlsx
@@ -62,7 +62,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.059.</t>
+          <t>-0.059*</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -314,7 +314,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>0.465</t>
         </is>
       </c>
     </row>
@@ -348,7 +348,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>9,548</t>
+          <t>9,549</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -358,7 +358,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7,919</t>
+          <t>7,920</t>
         </is>
       </c>
     </row>
